--- a/artfynd/A 49999-2025 artfynd.xlsx
+++ b/artfynd/A 49999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53776214</v>
+        <v>86162316</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,52 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vikingstads Utjord Klinttorp 1, 400m VSV, Vikingstad kyrka, Ög</t>
+          <t>Linköping, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525737.0462630227</v>
+        <v>525811</v>
       </c>
       <c r="R2" t="n">
-        <v>6469748.005918805</v>
+        <v>6469814</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +755,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-06-03</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-06-03</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,44 +785,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Milton</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Milton</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53775923</v>
+        <v>55592213</v>
       </c>
       <c r="B3" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -829,11 +827,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525737.0462630227</v>
+        <v>525737</v>
       </c>
       <c r="R3" t="n">
-        <v>6469748.005918805</v>
+        <v>6469748</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -871,22 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-06-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-06-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,32 +897,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55592213</v>
+        <v>53775923</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>221141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -948,7 +927,11 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525737.0462630227</v>
+        <v>525737</v>
       </c>
       <c r="R4" t="n">
-        <v>6469748.005918805</v>
+        <v>6469748</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -986,22 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-10-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-10-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,6 +998,110 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>53776214</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vikingstads Utjord Klinttorp 1, 400m VSV, Vikingstad kyrka, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>525737</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6469748</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vikingstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2015-06-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2015-06-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Milton</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Milton</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49999-2025 artfynd.xlsx
+++ b/artfynd/A 49999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55592213</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53775923</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53776214</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,8 +1122,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86162316</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>